--- a/important_mails_2026-04-24.xlsx
+++ b/important_mails_2026-04-24.xlsx
@@ -1502,7 +1502,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1517,77 +1517,21 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
+          <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
+          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家：
-我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
-【如何完成合规?】
-您必须与第三方检测、检验和认证服务提供商合作，对收到通知的所有 ASIN 进行商品检测或验证现有的检测文件。请按照以下步骤操作：
-1.前往【绩效】-【账户状况】-【政策合规性】，点击【食品和商品安全问题】。
-2.在【后续步骤】列下，针对需操作的商品点击【提交】-【验证您的商品】。
-3.从清单中选择第三方检测提供商（如需比价，可先查看【从多个提供商获取报价的说明】后再返回选择），点击继续。
-4.确认详细联系信息，点击【确认并继续】。
-5.复制生成的检测申请表编号，提供给所选提供商完成检测
-如果验证现有文件，您必须将由 ISO 17025 认可的实验室出具的检测报告提交至检测、检验和认证服务提供商。
-如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新” &gt; “验证您的商品”
-⚠️请注意：
-① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
-② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。再次提醒您，为避免下架，请在截止日期之前确保TRF状态更新为【正在验证】或【已通过】。
-③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
-感谢您的支持，祝您合规大卖！
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
-Amazon Global Selling Seller Compliance Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -1605,40 +1549,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -1656,39 +1600,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1705,39 +1649,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -1755,40 +1699,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1806,39 +1750,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -1856,39 +1800,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1905,39 +1849,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1952,39 +1896,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2003,39 +1947,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -2053,39 +1997,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -2124,39 +2068,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2172,40 +2116,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2221,39 +2165,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2269,39 +2213,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2315,40 +2259,40 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2364,39 +2308,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2412,39 +2356,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -2465,39 +2409,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2512,88 +2456,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Verify your primary operating address for tax purposes</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon Services
- Verify your primary operating address for tax purposes
- Hello,
-To ensure the pertinent tax treatment is applied to your account, you must confirm your primary operating address . To help you, we’ve introduced a new field in Seller Central, called primary operating address.
-This allows us to determine your establishment for tax purposes. If your information isn’t listed correctly, your taxes will also be incorrect.
- Your primary operating address or primary place of business is the physical location where you conduct your main day-to-day business activities. This can be either:
-- Where your central administration functions take place.
-- Where you have sufficient degree of permanence and an established presence in terms of human resources, technical resources, and infrastructure to run your business operations (e.g., where your employees are located).
- Here's how to verify your primary operating address:
-- Go to your Identity Information page .
-- If the pre-filled information is correct, click I confirm that my primary operating address is correct .
-- If it's incorrect, click Edit information and provide a valid primary operating address by selecting a saved address </t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2615,39 +2510,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2670,39 +2565,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -2711,39 +2606,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2763,39 +2658,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2821,39 +2716,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2874,39 +2769,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2932,39 +2827,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2984,40 +2879,40 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -3033,39 +2928,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3085,39 +2980,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3134,39 +3029,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3178,39 +3073,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3233,39 +3128,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3289,39 +3184,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3336,39 +3231,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3382,40 +3277,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3432,39 +3327,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3484,39 +3379,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3533,39 +3428,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3588,39 +3483,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3640,39 +3535,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3689,39 +3584,95 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家：
+我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
+【如何完成合规?】
+您必须与第三方检测、检验和认证服务提供商合作，对收到通知的所有 ASIN 进行商品检测或验证现有的检测文件。请按照以下步骤操作：
+1.前往【绩效】-【账户状况】-【政策合规性】，点击【食品和商品安全问题】。
+2.在【后续步骤】列下，针对需操作的商品点击【提交】-【验证您的商品】。
+3.从清单中选择第三方检测提供商（如需比价，可先查看【从多个提供商获取报价的说明】后再返回选择），点击继续。
+4.确认详细联系信息，点击【确认并继续】。
+5.复制生成的检测申请表编号，提供给所选提供商完成检测
+如果验证现有文件，您必须将由 ISO 17025 认可的实验室出具的检测报告提交至检测、检验和认证服务提供商。
+如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新” &gt; “验证您的商品”
+⚠️请注意：
+① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
+② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。再次提醒您，为避免下架，请在截止日期之前确保TRF状态更新为【正在验证】或【已通过】。
+③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
+感谢您的支持，祝您合规大卖！
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
+Amazon Global Selling Seller Compliance Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3740,39 +3691,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3788,39 +3739,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -3832,39 +3783,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3884,39 +3835,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3934,40 +3885,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3985,39 +3936,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4037,39 +3988,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4090,39 +4041,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4143,40 +4094,40 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -4192,39 +4143,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -4247,39 +4198,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4297,39 +4248,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4347,39 +4298,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -4399,39 +4350,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4449,39 +4400,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4499,39 +4450,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4549,39 +4500,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -4596,39 +4547,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4646,39 +4597,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4696,39 +4647,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4746,39 +4697,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4793,39 +4744,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4837,6 +4788,55 @@
 To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
 https://sellercentral.amazon.com/performance/account/health/compliance-request
 If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Verify your primary operating address for tax purposes</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ Verify your primary operating address for tax purposes
+ Hello,
+To ensure the pertinent tax treatment is applied to your account, you must confirm your primary operating address . To help you, we’ve introduced a new field in Seller Central, called primary operating address.
+This allows us to determine your establishment for tax purposes. If your information isn’t listed correctly, your taxes will also be incorrect.
+ Your primary operating address or primary place of business is the physical location where you conduct your main day-to-day business activities. This can be either:
+- Where your central administration functions take place.
+- Where you have sufficient degree of permanence and an established presence in terms of human resources, technical resources, and infrastructure to run your business operations (e.g., where your employees are located).
+ Here's how to verify your primary operating address:
+- Go to your Identity Information page .
+- If the pre-filled information is correct, click I confirm that my primary operating address is correct .
+- If it's incorrect, click Edit information and provide a valid primary operating address by selecting a saved address </t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-04-24.xlsx
+++ b/important_mails_2026-04-24.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,12 +531,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -546,21 +546,72 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
+          <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Balance paid on your Amazon seller account</t>
+          <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 05/23/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FD8VC559
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-105555325087061</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -576,39 +627,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -628,39 +679,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -677,39 +728,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -725,39 +776,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -777,39 +828,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -828,39 +879,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -879,39 +930,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -931,39 +982,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -992,39 +1043,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1042,39 +1093,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1092,39 +1143,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1142,39 +1193,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -1188,39 +1239,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1238,40 +1289,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1288,40 +1339,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1338,39 +1389,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -1404,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -1451,39 +1502,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -1499,39 +1550,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -1549,40 +1600,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -1600,39 +1651,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1649,39 +1700,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -1699,40 +1750,40 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1750,39 +1801,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -1800,39 +1851,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1849,39 +1900,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1896,39 +1947,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1947,39 +1998,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -1997,39 +2048,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -2068,39 +2119,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2116,40 +2167,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2165,39 +2216,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2213,39 +2264,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2259,40 +2310,40 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2308,39 +2359,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2356,39 +2407,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -2409,39 +2460,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2456,39 +2507,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2510,39 +2561,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2565,39 +2616,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -2606,39 +2657,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2658,39 +2709,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2716,39 +2767,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2769,39 +2820,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2827,39 +2878,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2879,40 +2930,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2925,58 +2976,6 @@
  Bonjour d’Amazon Services,
  Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.65 pour le règlement du solde de votre compte vendeur.
  Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (kpCypnMqWe)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1188095-0289626
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1372192148348110</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7438,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7454,68 +7453,21 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
+          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Votre paiement est en cours</t>
+          <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 03/25/26 15:00 CET, nous avons effectué un virement d’un montant de €
- 41.37 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de pér</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-23</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7536,39 +7488,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7591,39 +7543,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -7636,39 +7588,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7689,39 +7641,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7744,39 +7696,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7792,39 +7744,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -7840,39 +7792,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7892,39 +7844,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7943,39 +7895,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7984,39 +7936,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8034,39 +7986,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -8096,39 +8048,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
